--- a/reports/一级子公司A_利润表_2025-04.xlsx
+++ b/reports/一级子公司A_利润表_2025-04.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>171972935</v>
+        <v>174761398</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>167602139</v>
+        <v>166551404</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>627804143</v>
+        <v>626222825</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>678190</v>
+        <v>683597</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2555149</v>
+        <v>2559928</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>587118</v>
+        <v>592829</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2215153</v>
+        <v>2223546</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>499761</v>
+        <v>501744</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1876259</v>
+        <v>1885671</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>458350</v>
+        <v>460734</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1725770</v>
+        <v>1735141</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>250650</v>
+        <v>249834</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>938138</v>
+        <v>942648</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>199909</v>
+        <v>199447</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>750934</v>
+        <v>753458</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>169298957</v>
+        <v>172073213</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164928161</v>
+        <v>163863219</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84974258</v>
+        <v>84007322</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>318294911</v>
+        <v>317415576</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1556455</v>
+        <v>1542469</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>5841645</v>
+        <v>5813313</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1400466</v>
+        <v>1396794</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5274685</v>
+        <v>5247214</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75349032</v>
+        <v>75218752</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>282047040</v>
+        <v>281367010</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1592409</v>
+        <v>1605897</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>6020203</v>
+        <v>6007229</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>701205</v>
+        <v>703060</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2633869</v>
+        <v>2630137</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2486100</v>
+        <v>2513823</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>9400464</v>
+        <v>9413391</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1098669</v>
+        <v>1105756</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4132971</v>
+        <v>4142268</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4280952</v>
+        <v>4319886</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>16143897</v>
+        <v>16207827</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89844</v>
+        <v>90274</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>359333</v>
+        <v>361091</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2281913</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>8599527</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1517921</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5729870</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>114860320</v>
+        <v>121925631</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>102695958</v>
+        <v>101563136</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>100594159</v>
+        <v>99473617</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>376133743</v>
+        <v>375600882</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2101799</v>
+        <v>2089519</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>7905442</v>
+        <v>7879619</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3786127</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>14245907</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1213845</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4557584</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>760318</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2849402</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>914312</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3422107</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>686877</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2569625</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>458342</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1715373</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>381962</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1431267</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1750238</v>
+        <v>1757419</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>6570786</v>
+        <v>6597739</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1343551</v>
+        <v>1353519</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5066876</v>
+        <v>5092015</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1101731</v>
+        <v>1100721</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4127829</v>
+        <v>4148798</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8289677</v>
+        <v>8287000</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>31155990</v>
+        <v>31285797</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>351010</v>
+        <v>348820</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1398170</v>
+        <v>1318038</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>671706</v>
+        <v>666752</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2678801</v>
+        <v>2680864</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>761753</v>
+        <v>666752</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3040933</v>
+        <v>2680864</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90429</v>
+        <v>89564</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>360412</v>
+        <v>359256</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>340826</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1364006</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>664009</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2492455</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>228163</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>909372</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>171477</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>682578</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>286247</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1138965</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>954934</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3574325</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>152775</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>609021</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114467</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>457202</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>190453</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>762383</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>133033</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>533639</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>94817</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>380944</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>75713</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>304439</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>56718</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>228037</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>54438637</v>
+        <v>52489178</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>63080295</v>
+        <v>58724408</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>378784</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1424422</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>94885</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>378793</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>150153</v>
+        <v>150145</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>601102</v>
+        <v>598311</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>54288484</v>
+        <v>52717817</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5300335</v>
+        <v>5324010</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>21215141</v>
+        <v>21184292</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>48988149</v>
+        <v>47393807</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>48988149</v>
+        <v>47393807</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>48988149</v>
+        <v>47393807</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>48988149</v>
+        <v>47393807</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>48988149</v>
+        <v>47393807</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
